--- a/moduli_aziende/luppichiniulisse/moduli_compilati/MOD-870-B-Prodotti_Non_Conformi.xlsx
+++ b/moduli_aziende/luppichiniulisse/moduli_compilati/MOD-870-B-Prodotti_Non_Conformi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SW_Gestionali\Suite_9001_v4\moduli_compilati\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simoneleandrini\Documents\GitHub\SG_Viewer\moduli_aziende\luppichiniulisse\moduli_compilati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70311063-B5EB-47F1-A667-18CB6988E103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EAF1AC-6E0D-4FD8-BF9B-76793E24CC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
     <t>Data</t>
   </si>
@@ -52,9 +52,6 @@
     <t>ok</t>
   </si>
   <si>
-    <t>Centratori trave – Cliente El.En</t>
-  </si>
-  <si>
     <t>Graffi superficiali visibili su 5 pezzi dopo rientro da trattamento termico esterno. Difformità estetica e rischio compromissione funzionale su accoppiamento di precisione.</t>
   </si>
   <si>
@@ -76,9 +73,6 @@
     <t>attesa</t>
   </si>
   <si>
-    <t>Flangia supporto mandrino</t>
-  </si>
-  <si>
     <t>Diametro foro Ø32 H7 misurato Ø32.018 mm – fuori tolleranza superiore.</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
     <t>Rilavorazione</t>
   </si>
   <si>
-    <t>Corpo supporto lineare</t>
-  </si>
-  <si>
     <t>Programma CNC errato caricato su Hyundai; quota Z fuori specifica di 0.3 mm.</t>
   </si>
   <si>
@@ -118,9 +109,6 @@
     <t>Scarto parziale</t>
   </si>
   <si>
-    <t>Albero tornito C45</t>
-  </si>
-  <si>
     <t>Filettatura M24x1.5 incompleta su 3 pezzi; profondità filetto insufficiente.</t>
   </si>
   <si>
@@ -130,9 +118,6 @@
     <t>Sostituzione utensile; controllo 100% lotto successivo.</t>
   </si>
   <si>
-    <t>Piastra guida rettificata</t>
-  </si>
-  <si>
     <t>Rugosità Ra 2.4 rilevata; richiesta Ra 1.6.</t>
   </si>
   <si>
@@ -142,9 +127,6 @@
     <t>Regolazione parametri; controllo mola; nuova passata finitura.</t>
   </si>
   <si>
-    <t>Corpo valvola inox</t>
-  </si>
-  <si>
     <t>Marcatura laser con codice cliente errato.</t>
   </si>
   <si>
@@ -160,9 +142,6 @@
     <t>Recupero interno</t>
   </si>
   <si>
-    <t>Piastra accoppiamento</t>
-  </si>
-  <si>
     <t>Planarità 0.04 mm rilevata; richiesta 0.02 mm.</t>
   </si>
   <si>
@@ -172,9 +151,6 @@
     <t>Nuova passata finitura Mazak HCN 800; verifica staffaggio.</t>
   </si>
   <si>
-    <t>Timone direzione con albero A244</t>
-  </si>
-  <si>
     <t>Durezza/proprietà meccaniche non conformi a specifica tecnica a seguito lavorazione esterna di saldatura.</t>
   </si>
   <si>
@@ -196,9 +172,6 @@
     <t>RSG-QSA + AMM</t>
   </si>
   <si>
-    <t>Supporto Sensori</t>
-  </si>
-  <si>
     <t>Testa supporto non in tolleranza</t>
   </si>
   <si>
@@ -215,13 +188,16 @@
   </si>
   <si>
     <t>RSG-QSA + RDF OPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.. Dato non disponibile in modalità Ospite .. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,14 +207,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -281,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -290,7 +258,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -599,7 +566,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="155.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.5703125" bestFit="1" customWidth="1"/>
@@ -640,57 +607,57 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46038</v>
+        <v>46125</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46034</v>
+        <v>46093</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
       </c>
       <c r="I3" t="s">
         <v>9</v>
@@ -698,57 +665,57 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46031</v>
+        <v>46072</v>
       </c>
       <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
       <c r="H4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46043</v>
+        <v>46062</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I5" t="s">
         <v>9</v>
@@ -756,28 +723,28 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46040</v>
+        <v>46050</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
         <v>9</v>
@@ -788,25 +755,25 @@
         <v>46047</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
@@ -814,28 +781,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46049</v>
+        <v>46046</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
         <v>9</v>
@@ -843,28 +810,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46051</v>
+        <v>46046</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
         <v>48</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
       </c>
       <c r="I9" t="s">
         <v>9</v>
@@ -874,29 +841,29 @@
       <c r="A10" s="3">
         <v>45929</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>50</v>
+      <c r="B10" t="s">
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
